--- a/public/exports/70960516.xlsx
+++ b/public/exports/70960516.xlsx
@@ -9,7 +9,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:O70"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -24,55 +24,65 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Ejerskab</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primær registreret ejer</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Geografisk kommunekode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">Adresse</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t xml:space="preserve">Postnr.</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t xml:space="preserve">BFE-nummer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bygningsnummer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t xml:space="preserve">Areal (m²)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM-nummer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t xml:space="preserve">Energimærkningsfirma</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldig til</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler gyldigt mærke</t>
         </is>
@@ -91,53 +101,63 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gutfeldtsvej 2</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve">2366600</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>1278</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -156,53 +176,63 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gutfeldtsvej 6</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">2366726</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>1519</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -221,53 +251,63 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kokkedal Alle 9</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">717933, 2370872</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>427</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -286,53 +326,63 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Kokkedal Alle 9</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">717933, 2370872</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
         </is>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>366</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -351,53 +401,63 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rungsted Havn 1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve">717953, 2381215</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t xml:space="preserve">12</t>
         </is>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>1394</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -416,53 +476,63 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rungsted Havn 28</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">717965, 2381219</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve">13</t>
         </is>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>596</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -481,53 +551,63 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rungsted Strandvej 120</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">717951, 2380858</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>490</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -546,53 +626,63 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 7C</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stadionalle 11A</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717972, 2370956</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="H9">
-        <v>403</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9153682</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="J9">
+        <v>2969</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -611,53 +701,63 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 7D</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stadionalle 5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717971, 2370955</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="H10">
-        <v>1375</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9153682</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="J10">
+        <v>916</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -676,53 +776,63 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvemosen 5</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stadionalle 7C</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1310679</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H11">
-        <v>304</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717972, 2370956</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t xml:space="preserve">14</t>
+        </is>
+      </c>
+      <c r="J11">
+        <v>403</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -741,53 +851,63 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">Stadionalle 7D</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="H12">
-        <v>600</v>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717971, 2370955</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t xml:space="preserve">13</t>
+        </is>
+      </c>
+      <c r="J12">
+        <v>1375</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -806,53 +926,63 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">Stadionalle 8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
-        </is>
-      </c>
-      <c r="H13">
-        <v>454</v>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2381978</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="J13">
+        <v>2800</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -871,53 +1001,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 4E</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">Ulvemosen 5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
-        </is>
-      </c>
-      <c r="H14">
-        <v>294</v>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1310679</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J14">
+        <v>304</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t xml:space="preserve">Mangler energimærke</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -936,53 +1076,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 8</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381217, 100749912</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H15">
-        <v>363</v>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2369282</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">100144275</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BygTechA/S</t>
-        </is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="J15">
+        <v>600</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-10</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1001,53 +1151,63 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 7A</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">717973, 2370957</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="H16">
-        <v>3096</v>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2369282</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052253</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LuVa Consult APS</t>
-        </is>
+          <t xml:space="preserve">4</t>
+        </is>
+      </c>
+      <c r="J16">
+        <v>454</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-23</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1066,53 +1226,63 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 9</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">717970, 2370954</t>
+          <t xml:space="preserve">Ådalsparkvej 4E</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="H17">
-        <v>4496</v>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2369282</t>
+        </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056359</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LuVa Consult APS</t>
-        </is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="J17">
+        <v>294</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-30</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mangler energimærke</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1131,53 +1301,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 32</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rungsted Havn 8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717952, 2381218</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15</t>
-        </is>
-      </c>
-      <c r="H18">
-        <v>476</v>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2381217, 100749912</t>
+        </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">311065041</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CONSU bygningsrådgivning ApS</t>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J18">
+        <v>363</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07-16</t>
+          <t xml:space="preserve">100144275</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t xml:space="preserve">BygTechA/S</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2019-12-10</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t xml:space="preserve">Ja</t>
         </is>
@@ -1196,55 +1376,65 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 34</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stadionalle 7A</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717938, 7644227</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19</t>
-        </is>
-      </c>
-      <c r="H19">
-        <v>303</v>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717973, 2370957</t>
+        </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217548</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">BF Byggeservice ApS</t>
-        </is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="J19">
+        <v>3096</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">200052253</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">LuVa Consult APS</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">2021-08-23</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1261,55 +1451,65 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsvej 83</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2368570</t>
+          <t xml:space="preserve">Stadionalle 9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H20">
-        <v>341</v>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717970, 2370954</t>
+        </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239833</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Danakon a/s</t>
-        </is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="J20">
+        <v>4496</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">200056359</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">LuVa Consult APS</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">2021-12-30</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1326,55 +1526,65 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsvej 83</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2368570</t>
+          <t xml:space="preserve">Rungsted Havn 32</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H21">
-        <v>393</v>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717952, 2381218</t>
+        </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239833</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Danakon a/s</t>
-        </is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="J21">
+        <v>476</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">311065041</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">CONSU bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">2024-07-16</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Udløbet</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -1391,53 +1601,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Usserød Kongevej 45</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367843</t>
+          <t xml:space="preserve">Rungsted Havn 34</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H22">
-        <v>458</v>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">717938, 7644227</t>
+        </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259586</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Danakon a/s</t>
-        </is>
+          <t xml:space="preserve">19</t>
+        </is>
+      </c>
+      <c r="J22">
+        <v>303</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">311217548</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t xml:space="preserve">BF Byggeservice ApS</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-12-14</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1456,53 +1676,63 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50A</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alsvej 83</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2367722</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2368570</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H23">
-        <v>368</v>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311265087</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23">
+        <v>341</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311239833</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-09</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-04-07</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1521,53 +1751,63 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50B</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alsvej 83</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2367722</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2368570</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H24">
-        <v>669</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311265087</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24">
+        <v>393</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311239833</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-09</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-04-07</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1586,53 +1826,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50C</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sdr. Jagtvej 10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2367722</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3</t>
-        </is>
-      </c>
-      <c r="H25">
-        <v>500</v>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2367182</t>
+        </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265087</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J25">
+        <v>769</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311259590</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-09</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-07-07</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1651,53 +1901,63 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11A</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stadionalle 11B</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve">9153682</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="H26">
-        <v>2969</v>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265093</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+          <t xml:space="preserve">6</t>
+        </is>
+      </c>
+      <c r="J26">
+        <v>4057</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311259593</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-09</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-07-07</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1716,53 +1976,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11A</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">Usserød Kongevej 45</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
-        </is>
-      </c>
-      <c r="H27">
-        <v>6610</v>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2367843</t>
+        </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265093</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J27">
+        <v>458</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311259586</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-09</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-07-07</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1781,53 +2051,63 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11B</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">Ahornvej 50A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
-        </is>
-      </c>
-      <c r="H28">
-        <v>4057</v>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2367722</t>
+        </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265093</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J28">
+        <v>368</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311265087</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1846,53 +2126,63 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 5</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">Ahornvej 50B</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H29">
-        <v>6457</v>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2367722</t>
+        </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265093</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J29">
+        <v>669</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311265087</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1911,53 +2201,63 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 5</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">Ahornvej 50C</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
-        </is>
-      </c>
-      <c r="H30">
-        <v>916</v>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2367722</t>
+        </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265093</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
+          <t xml:space="preserve">3</t>
+        </is>
+      </c>
+      <c r="J30">
+        <v>500</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311265087</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -1976,53 +2276,63 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 5</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stadionalle 11A</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">9153682</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="H31">
-        <v>1595</v>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265093</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
+          <t xml:space="preserve">2</t>
+        </is>
+      </c>
+      <c r="J31">
+        <v>6610</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311265094</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2041,53 +2351,63 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 13</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366692</t>
+          <t xml:space="preserve">Stadionalle 5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9153682</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H32">
-        <v>613</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311265957</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32">
+        <v>6457</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311265099</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-14</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-08-09</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2106,53 +2426,63 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 31</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">Stadionalle 5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="H33">
-        <v>267</v>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9153682</t>
+        </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269866</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
+          <t xml:space="preserve">7</t>
+        </is>
+      </c>
+      <c r="J33">
+        <v>1595</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311265099</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-31</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-08-09</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2171,53 +2501,63 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Jagtvej 10</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Selmersvej 13</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2367182</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2366692</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H34">
-        <v>769</v>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311269865</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34">
+        <v>613</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311265957</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-08-31</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-08-14</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2236,53 +2576,63 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 4</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381983</t>
+          <t xml:space="preserve">Rungstedvej 31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="H35">
-        <v>521</v>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8101069</t>
+        </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270049</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="J35">
+        <v>267</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311269866</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2301,53 +2651,63 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekstorvet 1</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">246772</t>
+          <t xml:space="preserve">Stadionalle 4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t xml:space="preserve">2960</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2381983</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H36">
-        <v>5875</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311272829</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36">
+        <v>521</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311270049</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-09-14</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-08-31</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2366,53 +2726,63 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedal Stationsvej 3</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bibliotekstorvet 1</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2369157</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">246772</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H37">
-        <v>476</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311272832</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37">
+        <v>5875</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311272829</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-09-14</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2431,53 +2801,63 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breeltevej 3</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kokkedal Stationsvej 3</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100019618</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2369157</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H38">
-        <v>1306</v>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311279819</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38">
+        <v>476</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311272832</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-10-23</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
+      <c r="M38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-09-14</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2496,53 +2876,63 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 1</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Breeltevej 3</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2367211</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100019618</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H39">
-        <v>430</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311279821</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39">
+        <v>1306</v>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311279819</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2561,53 +2951,63 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 36</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gasværksvej 1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2366957</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2367211</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H40">
-        <v>744</v>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311286269</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40">
+        <v>430</v>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311279821</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2027-11-29</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2027-10-23</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2626,53 +3026,63 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophielund 25</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skovvænget 36</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2369150</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2366957</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H41">
-        <v>1941</v>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311286265</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
+      <c r="J41">
+        <v>744</v>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">311286269</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2691,53 +3101,63 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 8</t>
+          <t xml:space="preserve">Hørsholm Kommune</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">223</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">Sophielund 25</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
-        </is>
-      </c>
-      <c r="H42">
-        <v>2800</v>
+          <t xml:space="preserve">2970</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2369150</t>
+        </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286266</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="J42">
+        <v>1941</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
+          <t xml:space="preserve">311286265</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Danakon a/s</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2756,53 +3176,63 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rungstedvej 1</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve">2367324</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H43">
+      <c r="J43">
         <v>2151</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t xml:space="preserve">311288806</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2821,53 +3251,63 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ådalsvej 52</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve">2369817</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H44">
+      <c r="J44">
         <v>1351</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t xml:space="preserve">311288805</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2886,53 +3326,63 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ådalsvej 52</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t xml:space="preserve">2369817</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H45">
+      <c r="J45">
         <v>1171</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t xml:space="preserve">311288805</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -2951,53 +3401,63 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H46">
+      <c r="J46">
         <v>1691</v>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t xml:space="preserve">311289939</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3016,53 +3476,63 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H47">
+      <c r="J47">
         <v>3265</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t xml:space="preserve">311289940</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3081,53 +3551,63 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H48">
+      <c r="J48">
         <v>1610</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t xml:space="preserve">311289942</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3146,53 +3626,63 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="H49">
+      <c r="J49">
         <v>2388</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t xml:space="preserve">311289943</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3211,53 +3701,63 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t xml:space="preserve">8101069</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="H50">
+      <c r="J50">
         <v>474</v>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t xml:space="preserve">311289945</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3276,53 +3776,63 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H51">
+      <c r="J51">
         <v>8807</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t xml:space="preserve">311298940</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3341,53 +3851,63 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H52">
+      <c r="J52">
         <v>2450</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t xml:space="preserve">311298940</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3406,53 +3926,63 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H53">
+      <c r="J53">
         <v>1637</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t xml:space="preserve">311298938</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3471,53 +4001,63 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t xml:space="preserve">Stadionalle 12</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t xml:space="preserve">2381978</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H54">
+      <c r="J54">
         <v>6712</v>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t xml:space="preserve">311304707</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-03-23</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3536,53 +4076,63 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t xml:space="preserve">2380704</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H55">
+      <c r="J55">
         <v>1507</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t xml:space="preserve">311306137</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3601,53 +4151,63 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
           <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t xml:space="preserve">2380704</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H56">
+      <c r="J56">
         <v>2099</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t xml:space="preserve">311308266</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3666,53 +4226,63 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
           <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t xml:space="preserve">2380704</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H57">
+      <c r="J57">
         <v>3262</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t xml:space="preserve">311308262</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3731,53 +4301,63 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
           <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t xml:space="preserve">2960</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t xml:space="preserve">2380704</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H58">
+      <c r="J58">
         <v>614</v>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t xml:space="preserve">311308267</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3796,53 +4376,63 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t xml:space="preserve">Ådalsparkvej 4N</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t xml:space="preserve">2369282</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="H59">
+      <c r="J59">
         <v>408</v>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t xml:space="preserve">311420783</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t xml:space="preserve">2030-02-04</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3861,53 +4451,63 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
           <t xml:space="preserve">Rungstedvej 23</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t xml:space="preserve">2366696</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H60">
+      <c r="J60">
         <v>445</v>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t xml:space="preserve">311892520</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3926,53 +4526,63 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hørsholm Alle 4</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t xml:space="preserve">2367940</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H61">
+      <c r="J61">
         <v>350</v>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t xml:space="preserve">311893229</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -3991,53 +4601,63 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
           <t xml:space="preserve">Hørsholm Alle 4</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t xml:space="preserve">2367940</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H62">
+      <c r="J62">
         <v>2855</v>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t xml:space="preserve">311893225</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4056,53 +4676,63 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t xml:space="preserve">Mariehøj Alle 1</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t xml:space="preserve">7951098</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H63">
+      <c r="J63">
         <v>690</v>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t xml:space="preserve">311912380</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4121,53 +4751,63 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lundevej 26</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t xml:space="preserve">9153647</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H64">
+      <c r="J64">
         <v>840</v>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t xml:space="preserve">311915684</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4186,53 +4826,63 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="H65">
+      <c r="J65">
         <v>1343</v>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4251,53 +4901,63 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H66">
+      <c r="J66">
         <v>929</v>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4316,53 +4976,63 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="H67">
+      <c r="J67">
         <v>2007</v>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4381,53 +5051,63 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H68">
+      <c r="J68">
         <v>599</v>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4446,53 +5126,63 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="H69">
+      <c r="J69">
         <v>3389</v>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
@@ -4511,59 +5201,69 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">223</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
+          <t xml:space="preserve">Hørsholm Kommune</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
           <t xml:space="preserve">Lundevej 19</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t xml:space="preserve">2970</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t xml:space="preserve">7966206</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="H70">
+      <c r="J70">
         <v>2456</v>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t xml:space="preserve">311916600</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M70"/>
+  <autoFilter ref="A1:O70"/>
 </worksheet>
 </file>
--- a/public/exports/70960516.xlsx
+++ b/public/exports/70960516.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports/70960516.xlsx
+++ b/public/exports/70960516.xlsx
@@ -941,7 +941,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 8</t>
+          <t xml:space="preserve">Ulvemosen 5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -951,16 +951,16 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">1310679</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J13">
-        <v>2800</v>
+        <v>304</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1016,26 +1016,26 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ulvemosen 5</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1310679</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J14">
-        <v>304</v>
+        <v>600</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1106,11 +1106,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J15">
-        <v>600</v>
+        <v>454</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Ådalsparkvej 4E</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1181,11 +1181,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J16">
-        <v>454</v>
+        <v>294</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1241,45 +1241,45 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 4E</t>
+          <t xml:space="preserve">Rungsted Havn 8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">2381217, 100749912</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J17">
-        <v>294</v>
+        <v>363</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">100144275</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BygTechA/S</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-12-10</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 8</t>
+          <t xml:space="preserve">Stadionalle 7A</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1326,30 +1326,30 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381217, 100749912</t>
+          <t xml:space="preserve">717973, 2370957</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J18">
-        <v>363</v>
+        <v>3096</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t xml:space="preserve">100144275</t>
+          <t xml:space="preserve">200052253</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">BygTechA/S</t>
+          <t xml:space="preserve">LuVa Consult APS</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-10</t>
+          <t xml:space="preserve">2021-08-23</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 7A</t>
+          <t xml:space="preserve">Stadionalle 9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1401,20 +1401,20 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">717973, 2370957</t>
+          <t xml:space="preserve">717970, 2370954</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J19">
-        <v>3096</v>
+        <v>4496</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052253</t>
+          <t xml:space="preserve">200056359</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-23</t>
+          <t xml:space="preserve">2021-12-30</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 9</t>
+          <t xml:space="preserve">Rungsted Havn 32</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1476,30 +1476,30 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">717970, 2370954</t>
+          <t xml:space="preserve">717952, 2381218</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J20">
-        <v>4496</v>
+        <v>476</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056359</t>
+          <t xml:space="preserve">311065041</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuVa Consult APS</t>
+          <t xml:space="preserve">CONSU bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-12-30</t>
+          <t xml:space="preserve">2024-07-16</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 32</t>
+          <t xml:space="preserve">Rungsted Havn 34</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1551,40 +1551,40 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">717952, 2381218</t>
+          <t xml:space="preserve">717938, 7644227</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J21">
-        <v>476</v>
+        <v>303</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">311065041</t>
+          <t xml:space="preserve">311217548</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t xml:space="preserve">CONSU bygningsrådgivning ApS</t>
+          <t xml:space="preserve">BF Byggeservice ApS</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-07-16</t>
+          <t xml:space="preserve">2026-12-14</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -1616,40 +1616,40 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungsted Havn 34</t>
+          <t xml:space="preserve">Alsvej 83</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">717938, 7644227</t>
+          <t xml:space="preserve">2368570</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J22">
-        <v>303</v>
+        <v>341</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">311217548</t>
+          <t xml:space="preserve">311239833</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">BF Byggeservice ApS</t>
+          <t xml:space="preserve">Danakon a/s</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-14</t>
+          <t xml:space="preserve">2027-04-07</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1706,11 +1706,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J23">
-        <v>341</v>
+        <v>393</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alsvej 83</t>
+          <t xml:space="preserve">Sdr. Jagtvej 10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1776,20 +1776,20 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2368570</t>
+          <t xml:space="preserve">2367182</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J24">
-        <v>393</v>
+        <v>769</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">311239833</t>
+          <t xml:space="preserve">311259590</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-04-07</t>
+          <t xml:space="preserve">2027-07-07</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1841,30 +1841,30 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sdr. Jagtvej 10</t>
+          <t xml:space="preserve">Stadionalle 11B</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367182</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J25">
-        <v>769</v>
+        <v>4057</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259590</t>
+          <t xml:space="preserve">311259593</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1916,30 +1916,30 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11B</t>
+          <t xml:space="preserve">Usserød Kongevej 45</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">2367843</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J26">
-        <v>4057</v>
+        <v>458</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259593</t>
+          <t xml:space="preserve">311259586</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Usserød Kongevej 45</t>
+          <t xml:space="preserve">Ahornvej 50A</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367843</t>
+          <t xml:space="preserve">2367722</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2010,11 +2010,11 @@
         </is>
       </c>
       <c r="J27">
-        <v>458</v>
+        <v>368</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t xml:space="preserve">311259586</t>
+          <t xml:space="preserve">311265087</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-07</t>
+          <t xml:space="preserve">2027-08-09</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50A</t>
+          <t xml:space="preserve">Ahornvej 50B</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2081,11 +2081,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J28">
-        <v>368</v>
+        <v>669</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50B</t>
+          <t xml:space="preserve">Ahornvej 50C</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2156,11 +2156,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J29">
-        <v>669</v>
+        <v>500</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2216,30 +2216,30 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ahornvej 50C</t>
+          <t xml:space="preserve">Stadionalle 11A</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367722</t>
+          <t xml:space="preserve">9153682</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J30">
-        <v>500</v>
+        <v>6610</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265087</t>
+          <t xml:space="preserve">311265094</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 11A</t>
+          <t xml:space="preserve">Stadionalle 5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2306,15 +2306,15 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J31">
-        <v>6610</v>
+        <v>6457</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265094</t>
+          <t xml:space="preserve">311265099</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2381,11 +2381,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J32">
-        <v>6457</v>
+        <v>1595</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,30 +2441,30 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 5</t>
+          <t xml:space="preserve">Selmersvej 13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153682</t>
+          <t xml:space="preserve">2366692</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J33">
-        <v>1595</v>
+        <v>613</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265099</t>
+          <t xml:space="preserve">311265957</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-09</t>
+          <t xml:space="preserve">2027-08-14</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 13</t>
+          <t xml:space="preserve">Rungstedvej 31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,20 +2526,20 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366692</t>
+          <t xml:space="preserve">8101069</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J34">
-        <v>613</v>
+        <v>267</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t xml:space="preserve">311265957</t>
+          <t xml:space="preserve">311269866</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-14</t>
+          <t xml:space="preserve">2027-08-31</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -2591,30 +2591,30 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 31</t>
+          <t xml:space="preserve">Stadionalle 4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">2381983</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J35">
-        <v>267</v>
+        <v>521</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t xml:space="preserve">311269866</t>
+          <t xml:space="preserve">311270049</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 4</t>
+          <t xml:space="preserve">Bibliotekstorvet 1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381983</t>
+          <t xml:space="preserve">246772</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2685,11 +2685,11 @@
         </is>
       </c>
       <c r="J36">
-        <v>521</v>
+        <v>5875</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t xml:space="preserve">311270049</t>
+          <t xml:space="preserve">311272829</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-08-31</t>
+          <t xml:space="preserve">2027-09-14</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bibliotekstorvet 1</t>
+          <t xml:space="preserve">Kokkedal Stationsvej 3</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">246772</t>
+          <t xml:space="preserve">2369157</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2760,11 +2760,11 @@
         </is>
       </c>
       <c r="J37">
-        <v>5875</v>
+        <v>476</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272829</t>
+          <t xml:space="preserve">311272832</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kokkedal Stationsvej 3</t>
+          <t xml:space="preserve">Breeltevej 3</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369157</t>
+          <t xml:space="preserve">100019618</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2835,11 +2835,11 @@
         </is>
       </c>
       <c r="J38">
-        <v>476</v>
+        <v>1306</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t xml:space="preserve">311272832</t>
+          <t xml:space="preserve">311279819</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-09-14</t>
+          <t xml:space="preserve">2027-10-23</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Breeltevej 3</t>
+          <t xml:space="preserve">Gasværksvej 1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">100019618</t>
+          <t xml:space="preserve">2367211</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2910,11 +2910,11 @@
         </is>
       </c>
       <c r="J39">
-        <v>1306</v>
+        <v>430</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279819</t>
+          <t xml:space="preserve">311279821</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasværksvej 1</t>
+          <t xml:space="preserve">Skovvænget 36</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367211</t>
+          <t xml:space="preserve">2366957</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2985,11 +2985,11 @@
         </is>
       </c>
       <c r="J40">
-        <v>430</v>
+        <v>744</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279821</t>
+          <t xml:space="preserve">311286269</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-23</t>
+          <t xml:space="preserve">2027-11-29</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 36</t>
+          <t xml:space="preserve">Sophielund 25</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366957</t>
+          <t xml:space="preserve">2369150</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3060,11 +3060,11 @@
         </is>
       </c>
       <c r="J41">
-        <v>744</v>
+        <v>1941</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286269</t>
+          <t xml:space="preserve">311286265</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sophielund 25</t>
+          <t xml:space="preserve">Rungstedvej 1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369150</t>
+          <t xml:space="preserve">2367324</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3135,11 +3135,11 @@
         </is>
       </c>
       <c r="J42">
-        <v>1941</v>
+        <v>2151</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t xml:space="preserve">311286265</t>
+          <t xml:space="preserve">311288806</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-11-29</t>
+          <t xml:space="preserve">2027-12-14</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 1</t>
+          <t xml:space="preserve">Ådalsvej 52</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367324</t>
+          <t xml:space="preserve">2369817</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3210,11 +3210,11 @@
         </is>
       </c>
       <c r="J43">
-        <v>2151</v>
+        <v>1351</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288806</t>
+          <t xml:space="preserve">311288805</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3281,11 +3281,11 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J44">
-        <v>1351</v>
+        <v>1171</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsvej 52</t>
+          <t xml:space="preserve">Selmersvej 6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369817</t>
+          <t xml:space="preserve">8101069</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3360,11 +3360,11 @@
         </is>
       </c>
       <c r="J45">
-        <v>1171</v>
+        <v>1691</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t xml:space="preserve">311288805</t>
+          <t xml:space="preserve">311289939</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-14</t>
+          <t xml:space="preserve">2027-12-21</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3431,15 +3431,15 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J46">
-        <v>1691</v>
+        <v>3265</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289939</t>
+          <t xml:space="preserve">311289940</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3506,15 +3506,15 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J47">
-        <v>3265</v>
+        <v>1610</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289940</t>
+          <t xml:space="preserve">311289942</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3581,15 +3581,15 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J48">
-        <v>1610</v>
+        <v>2388</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289942</t>
+          <t xml:space="preserve">311289943</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3656,15 +3656,15 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J49">
-        <v>2388</v>
+        <v>474</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289943</t>
+          <t xml:space="preserve">311289945</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Selmersvej 6</t>
+          <t xml:space="preserve">Ådalsparkvej 2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,20 +3726,20 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8101069</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J50">
-        <v>474</v>
+        <v>8807</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289945</t>
+          <t xml:space="preserve">311298940</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-21</t>
+          <t xml:space="preserve">2028-02-21</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3806,11 +3806,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J51">
-        <v>8807</v>
+        <v>2450</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3881,15 +3881,15 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J52">
-        <v>2450</v>
+        <v>1637</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298940</t>
+          <t xml:space="preserve">311298938</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3941,30 +3941,30 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 2</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J53">
-        <v>1637</v>
+        <v>1507</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t xml:space="preserve">311298938</t>
+          <t xml:space="preserve">311306137</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3974,7 +3974,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-21</t>
+          <t xml:space="preserve">2028-04-03</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionalle 12</t>
+          <t xml:space="preserve">Østre Stationsvej 1A</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2381978</t>
+          <t xml:space="preserve">2380704</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4035,11 +4035,11 @@
         </is>
       </c>
       <c r="J54">
-        <v>6712</v>
+        <v>2099</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t xml:space="preserve">311304707</t>
+          <t xml:space="preserve">311308266</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4049,7 +4049,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-03-23</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4106,15 +4106,15 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J55">
-        <v>1507</v>
+        <v>3262</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t xml:space="preserve">311306137</t>
+          <t xml:space="preserve">311308262</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-03</t>
+          <t xml:space="preserve">2028-04-13</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4181,15 +4181,15 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J56">
-        <v>2099</v>
+        <v>614</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308266</t>
+          <t xml:space="preserve">311308267</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4241,40 +4241,40 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Ådalsparkvej 4N</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">2369282</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J57">
-        <v>3262</v>
+        <v>408</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308262</t>
+          <t xml:space="preserve">311420783</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2030-02-04</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4316,40 +4316,40 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Stationsvej 1A</t>
+          <t xml:space="preserve">Rungstedvej 23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2960</t>
+          <t xml:space="preserve">2970</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380704</t>
+          <t xml:space="preserve">2366696</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J58">
-        <v>614</v>
+        <v>445</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311308267</t>
+          <t xml:space="preserve">311892520</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danakon a/s</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-04-13</t>
+          <t xml:space="preserve">2036-04-08</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalsparkvej 4N</t>
+          <t xml:space="preserve">Hørsholm Alle 4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -4401,30 +4401,30 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2369282</t>
+          <t xml:space="preserve">2367940</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J59">
-        <v>408</v>
+        <v>350</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420783</t>
+          <t xml:space="preserve">311893229</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topdahl Energirådgivere ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-04</t>
+          <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rungstedvej 23</t>
+          <t xml:space="preserve">Hørsholm Alle 4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4476,20 +4476,20 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2366696</t>
+          <t xml:space="preserve">2367940</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J60">
-        <v>445</v>
+        <v>2855</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t xml:space="preserve">311892520</t>
+          <t xml:space="preserve">311893225</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-08</t>
+          <t xml:space="preserve">2036-04-10</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Alle 4</t>
+          <t xml:space="preserve">Mariehøj Alle 1</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367940</t>
+          <t xml:space="preserve">7951098</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,11 +4560,11 @@
         </is>
       </c>
       <c r="J61">
-        <v>350</v>
+        <v>690</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893229</t>
+          <t xml:space="preserve">311912380</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-10</t>
+          <t xml:space="preserve">2036-07-02</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hørsholm Alle 4</t>
+          <t xml:space="preserve">Lundevej 26</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4626,20 +4626,20 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2367940</t>
+          <t xml:space="preserve">9153647</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>2855</v>
+        <v>840</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t xml:space="preserve">311893225</t>
+          <t xml:space="preserve">311915684</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-04-10</t>
+          <t xml:space="preserve">2036-07-23</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mariehøj Alle 1</t>
+          <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">7951098</t>
+          <t xml:space="preserve">7966206</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,11 +4710,11 @@
         </is>
       </c>
       <c r="J63">
-        <v>690</v>
+        <v>1343</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t xml:space="preserve">311912380</t>
+          <t xml:space="preserve">311916600</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-02</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 26</t>
+          <t xml:space="preserve">Gl Byvej 10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4776,20 +4776,20 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">9153647</t>
+          <t xml:space="preserve">7966206</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J64">
-        <v>840</v>
+        <v>929</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t xml:space="preserve">311915684</t>
+          <t xml:space="preserve">311916600</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-23</t>
+          <t xml:space="preserve">2036-07-30</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4856,11 +4856,11 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J65">
-        <v>1343</v>
+        <v>2007</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4931,11 +4931,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J66">
-        <v>929</v>
+        <v>599</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5006,11 +5006,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J67">
-        <v>2007</v>
+        <v>3389</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Byvej 10</t>
+          <t xml:space="preserve">Lundevej 19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5081,11 +5081,11 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J68">
-        <v>599</v>
+        <v>2456</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5141,30 +5141,30 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl Byvej 10</t>
+          <t xml:space="preserve">Stadionalle 12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966206</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J69">
-        <v>3389</v>
+        <v>6712</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916600</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5216,30 +5216,30 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundevej 19</t>
+          <t xml:space="preserve">Stadionalle 8</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2970</t>
+          <t xml:space="preserve">2960</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">7966206</t>
+          <t xml:space="preserve">2381978</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J70">
-        <v>2456</v>
+        <v>2800</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916600</t>
+          <t xml:space="preserve">311931619</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-30</t>
+          <t xml:space="preserve">2036-10-13</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
